--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486396_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486396_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0735</v>
+        <v>3.3763</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4615</v>
+        <v>2.2126</v>
       </c>
       <c r="F2" t="n">
-        <v>1.612</v>
+        <v>1.1637</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5359</v>
+        <v>2.6782</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8937</v>
+        <v>3.6464</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3578</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>4.018</v>
+        <v>1.9803</v>
       </c>
       <c r="K2" t="n">
-        <v>4.018</v>
+        <v>2.2082</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0.2279</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5178</v>
+        <v>0.6979</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8757</v>
+        <v>1.4382</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3578</v>
+        <v>-0.7403</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R2" t="n">
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3201</v>
+        <v>-0.6684</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3581</v>
+        <v>-0.6801</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.038</v>
+        <v>0.0117</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.13</v>
+        <v>0.0615</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3904</v>
+        <v>-1.0684</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0102</v>
+        <v>2.665</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8773</v>
+        <v>1.238</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1329</v>
+        <v>1.427</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6782</v>
+        <v>4.5359</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6464</v>
+        <v>4.8937</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.3578</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9803</v>
+        <v>4.018</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2082</v>
+        <v>4.018</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2279</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6979</v>
+        <v>0.5178</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4382</v>
+        <v>0.8757</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7403</v>
+        <v>-0.3578</v>
       </c>
       <c r="P3" t="n">
-        <v>1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0345</v>
+        <v>-0.0883</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0154</v>
+        <v>0.1346</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0191</v>
+        <v>-0.2229</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0615</v>
+        <v>-1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0684</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0577</v>
+        <v>2.5672</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.197</v>
+        <v>1.459</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2547</v>
+        <v>1.1081</v>
       </c>
       <c r="G4" t="n">
-        <v>0.097</v>
+        <v>3.6182</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7457</v>
+        <v>3.419</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6487</v>
+        <v>0.1992</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1834</v>
+        <v>1.5258</v>
       </c>
       <c r="K4" t="n">
-        <v>0.192</v>
+        <v>2.0963</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3754</v>
+        <v>-0.5705</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2804</v>
+        <v>2.0924</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5538</v>
+        <v>1.3227</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2733</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3081</v>
+        <v>-1.1608</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1214</v>
+        <v>-0.4566</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4295</v>
+        <v>-0.7042</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>1.695</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7602</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6385</v>
+        <v>1.6763</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9002</v>
+        <v>-0.0853</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7382</v>
+        <v>1.7615</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6182</v>
+        <v>0.097</v>
       </c>
       <c r="H5" t="n">
-        <v>3.419</v>
+        <v>1.7457</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1992</v>
+        <v>-1.6487</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5258</v>
+        <v>-1.1834</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0963</v>
+        <v>0.192</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5705</v>
+        <v>-1.3754</v>
       </c>
       <c r="M5" t="n">
-        <v>2.0924</v>
+        <v>1.2804</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3227</v>
+        <v>1.5538</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7697000000000001</v>
+        <v>-0.2733</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.0895</v>
+        <v>-0.0733</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0154</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0741</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="V5" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.3252</v>
+      </c>
+      <c r="X5" t="n">
         <v>-0.7602</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-2.4552</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7947</v>
+        <v>0.2779</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1709</v>
+        <v>-0.6826</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9656</v>
+        <v>0.9604</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8971</v>
+        <v>0.4602</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4425</v>
+        <v>2.6428</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.3396</v>
+        <v>-2.1826</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1591</v>
+        <v>0.7943</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0378</v>
+        <v>0.7911</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.1969</v>
+        <v>0.0032</v>
       </c>
       <c r="M6" t="n">
-        <v>0.262</v>
+        <v>-0.334</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4047</v>
+        <v>1.8518</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1427</v>
+        <v>-2.1858</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2175</v>
+        <v>-0.9394</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9458</v>
+        <v>-0.1718</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7282</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8218</v>
+        <v>-0.113</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3082</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0381</v>
+        <v>-0.0994</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9061</v>
+        <v>-1.065</v>
       </c>
       <c r="F7" t="n">
-        <v>0.868</v>
+        <v>0.9656</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4602</v>
+        <v>-0.8971</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6428</v>
+        <v>2.4425</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1826</v>
+        <v>-3.3396</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7943</v>
+        <v>-1.1591</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7911</v>
+        <v>1.0378</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0032</v>
+        <v>-2.1969</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.334</v>
+        <v>0.262</v>
       </c>
       <c r="N7" t="n">
-        <v>1.8518</v>
+        <v>1.4047</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1858</v>
+        <v>-1.1427</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2554</v>
+        <v>-0.6766</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3953</v>
+        <v>0.0517</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8601</v>
+        <v>-0.7282</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.113</v>
+        <v>0.8218</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.113</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7695</v>
+        <v>-2.0528</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3958</v>
+        <v>-2.4016</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6262</v>
+        <v>0.3488</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8762</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1321</v>
+        <v>-0.1511</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0022</v>
+        <v>-0.0036</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1299</v>
+        <v>-0.1475</v>
       </c>
       <c r="V8" t="n">
         <v>-0.678</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0981</v>
+        <v>-2.7417</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.501</v>
+        <v>-2.6069</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5972</v>
+        <v>-0.1348</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3561</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1288</v>
+        <v>-0.7724</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1524</v>
+        <v>-0.2584</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9764</v>
+        <v>-0.514</v>
       </c>
       <c r="V9" t="n">
         <v>0.8218</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>5.668900000000002</v>
+        <v>5.668800000000001</v>
       </c>
       <c r="E10" t="n">
         <v>-1.9318</v>
       </c>
       <c r="F10" t="n">
-        <v>7.6004</v>
+        <v>7.600300000000001</v>
       </c>
       <c r="G10" t="n">
         <v>6.2601</v>
@@ -1234,13 +1234,13 @@
         <v>11.9628</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.5304</v>
+        <v>-4.5303</v>
       </c>
       <c r="T10" t="n">
         <v>-1.3938</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.1365</v>
+        <v>-3.1364</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4110999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.7265</v>
+        <v>4.8685</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7646</v>
+        <v>3.5469</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9619</v>
+        <v>1.3216</v>
       </c>
       <c r="G11" t="n">
         <v>3.8464</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2075</v>
+        <v>-0.0655</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1284</v>
+        <v>-0.3461</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0791</v>
+        <v>0.2806</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7046</v>
+        <v>3.1685</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4169</v>
+        <v>1.9383</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7122000000000001</v>
+        <v>1.2302</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5594</v>
+        <v>0.7275</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.879</v>
+        <v>-0.9977</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4384</v>
+        <v>1.7252</v>
       </c>
       <c r="J12" t="n">
-        <v>0.64</v>
+        <v>0.9357</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7752</v>
+        <v>-0.5959</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4152</v>
+        <v>1.5316</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9194</v>
+        <v>-0.2082</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1038</v>
+        <v>-0.4018</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0231</v>
+        <v>0.1936</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3622</v>
+        <v>0.441</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3864</v>
+        <v>-0.1274</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0242</v>
+        <v>0.5684</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8695</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4723</v>
+        <v>1.6351</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2678</v>
+        <v>2.0699</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2045</v>
+        <v>-0.4348</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7275</v>
+        <v>1.5594</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9977</v>
+        <v>-0.879</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7252</v>
+        <v>2.4384</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9357</v>
+        <v>0.64</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5959</v>
+        <v>-0.7752</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5316</v>
+        <v>1.4152</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2082</v>
+        <v>0.9194</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4018</v>
+        <v>-0.1038</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1936</v>
+        <v>1.0231</v>
       </c>
       <c r="P13" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2552</v>
+        <v>1.2927</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7979000000000001</v>
+        <v>1.0395</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5427</v>
+        <v>0.2532</v>
       </c>
       <c r="V13" t="n">
-        <v>1.13</v>
+        <v>-1.8695</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6006</v>
+        <v>1.0418</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0065</v>
+        <v>0.4477</v>
       </c>
       <c r="F14" t="n">
         <v>0.5941</v>
@@ -1546,10 +1546,10 @@
         <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3531</v>
+        <v>0.7943</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1596</v>
+        <v>0.6009</v>
       </c>
       <c r="U14" t="n">
         <v>0.1935</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6857</v>
+        <v>0.3561</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2383</v>
+        <v>-0.6795</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5526</v>
+        <v>1.0356</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5965</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6542</v>
+        <v>0.3876</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3148</v>
+        <v>0.244</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3394</v>
+        <v>0.1436</v>
       </c>
       <c r="V15" t="n">
         <v>0.5649999999999999</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.4007</v>
+        <v>-2.555</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.9691</v>
+        <v>-0.7453</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5684</v>
+        <v>-1.8097</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.37</v>
+        <v>-2.8895</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.652</v>
+        <v>-2.8712</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2821</v>
+        <v>-0.0183</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1697</v>
+        <v>-0.7593</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3227</v>
+        <v>-1.1434</v>
       </c>
       <c r="L16" t="n">
-        <v>0.153</v>
+        <v>0.3841</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2003</v>
+        <v>-2.1302</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3293</v>
+        <v>-1.7278</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1291</v>
+        <v>-0.4024</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2743</v>
+        <v>0.4873</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1152</v>
+        <v>-0.0709</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1591</v>
+        <v>0.5582</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7395</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7395</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.0663</v>
+        <v>-2.8464</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4158</v>
+        <v>-3.5279</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6505</v>
+        <v>0.6815</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.8895</v>
+        <v>-2.37</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.8712</v>
+        <v>-2.652</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0183</v>
+        <v>0.2821</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7593</v>
+        <v>-1.1697</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1434</v>
+        <v>-1.3227</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3841</v>
+        <v>0.153</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1302</v>
+        <v>-1.2003</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7278</v>
+        <v>-1.3293</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4024</v>
+        <v>0.1291</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.024</v>
+        <v>0.8286</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.5564</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7174</v>
+        <v>0.2722</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2599</v>
+        <v>-0.7395</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3252</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.1981</v>
+        <v>-4.3705</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.9472</v>
+        <v>-3.368</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7492</v>
+        <v>-1.0025</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8691</v>
+        <v>-4.2635</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.1243</v>
+        <v>-0.9613</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2552</v>
+        <v>-3.3022</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.8546</v>
+        <v>-3.2919</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.4061</v>
+        <v>0.2039</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5515</v>
+        <v>-3.4958</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9854000000000001</v>
+        <v>-0.9716</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-1.1652</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7037</v>
+        <v>0.1936</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.5676</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.4377</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>1.783</v>
+        <v>0.3503</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3243</v>
+        <v>0.2512</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4587</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5443</v>
+        <v>0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0207</v>
+        <v>0.7602</v>
       </c>
       <c r="X18" t="n">
         <v>-0.5649999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.822</v>
+        <v>-5.4768</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.4856</v>
+        <v>-7.2825</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3364</v>
+        <v>1.8057</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.2635</v>
+        <v>-1.8691</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9613</v>
+        <v>-5.1243</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.3022</v>
+        <v>3.2552</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.2919</v>
+        <v>-2.8546</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2039</v>
+        <v>-4.4061</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.4958</v>
+        <v>1.5515</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9716</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1652</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1936</v>
+        <v>1.7037</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>-4.5676</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-5.4377</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1012</v>
+        <v>1.5042</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.989</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2348</v>
+        <v>0.5152</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1952</v>
+        <v>-0.5443</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7602</v>
+        <v>0.0207</v>
       </c>
       <c r="X19" t="n">
         <v>-0.5649999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.668799999999998</v>
+        <v>-4.178700000000002</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.600199999999999</v>
+        <v>-7.600399999999998</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9316</v>
+        <v>3.4217</v>
       </c>
       <c r="G20" t="n">
         <v>-6.260299999999999</v>
@@ -1993,7 +1993,7 @@
         <v>-10.9919</v>
       </c>
       <c r="L20" t="n">
-        <v>6.136000000000002</v>
+        <v>6.136</v>
       </c>
       <c r="M20" t="n">
         <v>-1.4044</v>
@@ -2002,7 +2002,7 @@
         <v>-7.1654</v>
       </c>
       <c r="O20" t="n">
-        <v>5.7612</v>
+        <v>5.761200000000001</v>
       </c>
       <c r="P20" t="n">
         <v>-4.350099999999999</v>
@@ -2014,19 +2014,19 @@
         <v>7.6125</v>
       </c>
       <c r="S20" t="n">
-        <v>4.5305</v>
+        <v>6.020499999999999</v>
       </c>
       <c r="T20" t="n">
         <v>3.1366</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3939</v>
+        <v>2.884</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4110999999999999</v>
+        <v>0.4110999999999998</v>
       </c>
       <c r="W20" t="n">
-        <v>6.081700000000001</v>
+        <v>6.0817</v>
       </c>
       <c r="X20" t="n">
         <v>-5.670599999999999</v>
